--- a/Pipe_Matlab_Indici_di_Prestazione_Guasto_AGV/FOLDER/EXCEL.xlsx
+++ b/Pipe_Matlab_Indici_di_Prestazione_Guasto_AGV/FOLDER/EXCEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lachiara\Documents\GitHub\ControlloAvanzato\Pipe_Matlab_Indici_di_Prestazione_Guasto_AGV\FOLDER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6B6976-FB20-46D4-A20D-721CB23651B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B71DC4E-CBA7-45FB-8A9B-02E3F074F20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -8669,7 +8669,7 @@
         <v>1</v>
       </c>
       <c r="J133" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K133" s="5">
         <v>0</v>
@@ -8764,7 +8764,7 @@
         <v>1</v>
       </c>
       <c r="J134" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K134" s="6">
         <v>0</v>
